--- a/04_DESIGN_TABLES/DesignTable_2500.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2500.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -541,6 +541,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2125,24 +2130,50 @@
           <t>2500-06-04-FG</t>
         </is>
       </c>
+      <c r="B30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.172</v>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>2500-06-04-FG</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>9/16-18 x 7/16-20 (male JIC both ends)</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2500-06-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-20] OMi catalog SKU; legs M1 / M2, flats Y, bores D1 / D2: Brennan TFA catalog p.22 (TFA-p022-t02 "2500-FG MJ-MJ 90 DEG ELBOW") - Air-Way s117 prints only the non-forged 2500-06-04 M1 1.08 / M2 0.95 / Y 0.63 (forged rule: a -FG row is not built from the non-forged twin), OMi Items row 641 has no dimensions; JIC ends MS33656J (end library)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2500-06-04 dims are NOT assumed; confirm before modelling</t>
+          <t>2026-10-20 (batch 19 E_gen, A7): sizes from the Brennan TFA catalog p.22, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING). Air-Way non-forged twin differs: 2500-06-04 M1 1.08 / M2 0.95 / Y 0.63</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2153,6 +2184,11 @@
       <c r="O30" t="inlineStr">
         <is>
           <t>2500-06-04-FG</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2162,24 +2198,50 @@
           <t>2500-08-06-FG</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.297</v>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>2500-08-06-FG</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>3/4-16 x 9/16-18 (male JIC both ends)</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2500-08-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-20] OMi catalog SKU; legs M1 / M2, flats Y, bores D1 / D2: Brennan TFA catalog p.22 (TFA-p022-t02 "2500-FG MJ-MJ 90 DEG ELBOW") - Air-Way s117 prints only the non-forged 2500-08-06 M1 1.25 / M2 1.15 / Y 0.81 (forged rule: a -FG row is not built from the non-forged twin), OMi Items row 643 has no dimensions; JIC ends MS33656J (end library)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2500-08-06 dims are NOT assumed; confirm before modelling</t>
+          <t>2026-10-20 (batch 19 E_gen, A7): sizes from the Brennan TFA catalog p.22, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING). Air-Way non-forged twin differs: 2500-08-06 M1 1.25 / M2 1.15 / Y 0.81</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2190,6 +2252,11 @@
       <c r="O31" t="inlineStr">
         <is>
           <t>2500-08-06-FG</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2199,24 +2266,50 @@
           <t>2500-12-08-FG</t>
         </is>
       </c>
+      <c r="B32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.391</v>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>2500-12-08-FG</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1 1/16-12 x 3/4-16 (male JIC both ends)</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2500-12-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-20] OMi catalog SKU; legs M1 / M2, flats Y, bores D1 / D2: Brennan TFA catalog p.22 (TFA-p022-t02 "2500-FG MJ-MJ 90 DEG ELBOW") - Air-Way s117 prints only the non-forged 2500-12-08 M1 1.66 / M2 1.40 / Y 1.13 (forged rule: a -FG row is not built from the non-forged twin), OMi Items row 647 has no dimensions; JIC ends MS33656J (end library)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2500-12-08 dims are NOT assumed; confirm before modelling</t>
+          <t>2026-10-20 (batch 19 E_gen, A7): sizes from the Brennan TFA catalog p.22, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING). Air-Way non-forged twin differs: 2500-12-08 M1 1.66 / M2 1.40 / Y 1.13</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2227,6 +2320,11 @@
       <c r="O32" t="inlineStr">
         <is>
           <t>2500-12-08-FG</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2236,24 +2334,50 @@
           <t>2500-12-10-FG</t>
         </is>
       </c>
+      <c r="B33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.484</v>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>2500-12-10-FG</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1 1/16-12 x 7/8-14 (male JIC both ends)</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2500-12-10 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-20] OMi catalog SKU; legs M1 / M2, flats Y, bores D1 / D2: Brennan TFA catalog p.22 (TFA-p022-t02 "2500-FG MJ-MJ 90 DEG ELBOW") - Air-Way s117 prints only the non-forged 2500-12-10 M1 1.66 / M2 1.55 / Y 1.13 (forged rule: a -FG row is not built from the non-forged twin), OMi Items row 648 has no dimensions; JIC ends MS33656J (end library)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2500-12-10 dims are NOT assumed; confirm before modelling</t>
+          <t>2026-10-20 (batch 19 E_gen, A7): sizes from the Brennan TFA catalog p.22, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING). Air-Way non-forged twin differs: 2500-12-10 M1 1.66 / M2 1.55 / Y 1.13</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2264,6 +2388,11 @@
       <c r="O33" t="inlineStr">
         <is>
           <t>2500-12-10-FG</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
